--- a/input/excel/Profile and ValueSet_ServiceRequest_Lab_16.01.2026/SRLabResearchs.xlsx
+++ b/input/excel/Profile and ValueSet_ServiceRequest_Lab_16.01.2026/SRLabResearchs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\behzod_axmedov\Desktop\DHP-temp02\UZCoreServiceRequest_Lab\digital-health-ig\input\excel\Profile and ValueSet_ServiceRequest_Lab_16.01.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116F33E1-912C-4FEA-A3BA-95D1DF8B265A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC856132-59B7-44C2-992F-61A5BFBADFAA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="19050" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8640" yWindow="1440" windowWidth="19050" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -2776,9 +2776,6 @@
     <t>Cytoplasmic maturation index of erythroid cells in Bone marrow</t>
   </si>
   <si>
-    <t>lab-P</t>
-  </si>
-  <si>
     <t>29610-3</t>
   </si>
   <si>
@@ -2791,9 +2788,6 @@
     <t>Hepatitis B virus DNA [Presence] in Serum or Plasma by NAA with probe detection</t>
   </si>
   <si>
-    <t>lab-Q</t>
-  </si>
-  <si>
     <t>42595-9</t>
   </si>
   <si>
@@ -2806,9 +2800,6 @@
     <t>Hepatitis B virus DNA [Units/volume] (viral load) in Serum or Plasma by NAA with probe detection</t>
   </si>
   <si>
-    <t>lab-R</t>
-  </si>
-  <si>
     <t>11259-9</t>
   </si>
   <si>
@@ -2821,9 +2812,6 @@
     <t>Hepatitis C virus RNA [Presence] in Serum or Plasma by NAA with probe detection</t>
   </si>
   <si>
-    <t>lab-S</t>
-  </si>
-  <si>
     <t>11011-4</t>
   </si>
   <si>
@@ -2836,9 +2824,6 @@
     <t>Hepatitis C virus RNA [Units/volume] (viral load) in Serum or Plasma by NAA with probe detection</t>
   </si>
   <si>
-    <t>lab-T</t>
-  </si>
-  <si>
     <t>32286-7</t>
   </si>
   <si>
@@ -2851,9 +2836,6 @@
     <t>Hepatitis C virus genotype [Identifier] in Serum or Plasma by NAA with probe detection</t>
   </si>
   <si>
-    <t>lab-U</t>
-  </si>
-  <si>
     <t>7906-1</t>
   </si>
   <si>
@@ -2866,9 +2848,6 @@
     <t>Hepatitis D virus RNA [Presence] in Serum or Plasma by NAA with probe detection</t>
   </si>
   <si>
-    <t>lab-V</t>
-  </si>
-  <si>
     <t>85512-2</t>
   </si>
   <si>
@@ -2879,9 +2858,6 @@
   </si>
   <si>
     <t>Hepatitis D virus RNA [Units/volume] (viral load) in Serum or Plasma by NAA with probe detection</t>
-  </si>
-  <si>
-    <t>lab-W</t>
   </si>
   <si>
     <t>22327-1</t>
@@ -2918,9 +2894,6 @@
     <t>Hepatitis C virus Ab [Units/volume] in Serum</t>
   </si>
   <si>
-    <t>lab-X</t>
-  </si>
-  <si>
     <t>5195-3</t>
   </si>
   <si>
@@ -2933,9 +2906,6 @@
     <t>Hepatitis B virus surface Ag [Presence] in Serum or Plasma</t>
   </si>
   <si>
-    <t>lab-Y</t>
-  </si>
-  <si>
     <t>22322-2</t>
   </si>
   <si>
@@ -2948,9 +2918,6 @@
     <t>Hepatitis B virus surface Ab [Presence] in Serum</t>
   </si>
   <si>
-    <t>lab-Z</t>
-  </si>
-  <si>
     <t>Gepatit B virusining yuzaki antigeni — HBsAg</t>
   </si>
   <si>
@@ -2960,9 +2927,6 @@
     <t>Hepatitis B virus surface Ag [Presence] in Serum</t>
   </si>
   <si>
-    <t>lab-AA</t>
-  </si>
-  <si>
     <t>13955-0</t>
   </si>
   <si>
@@ -2975,9 +2939,6 @@
     <t>Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
   </si>
   <si>
-    <t>lab-BB</t>
-  </si>
-  <si>
     <t>13952-7</t>
   </si>
   <si>
@@ -2990,9 +2951,6 @@
     <t>Hepatitis B virus (HBV) Core antibody, Blood</t>
   </si>
   <si>
-    <t>lab-CC</t>
-  </si>
-  <si>
     <t>13954-3</t>
   </si>
   <si>
@@ -3005,9 +2963,6 @@
     <t>Hepatitis B virus e Ag [Presence] in Serum or Plasma</t>
   </si>
   <si>
-    <t>lab-DD</t>
-  </si>
-  <si>
     <t xml:space="preserve">22314-9 </t>
   </si>
   <si>
@@ -3020,9 +2975,6 @@
     <t>Hepatitis A virus IgM Ab [Presence] in Serum</t>
   </si>
   <si>
-    <t>lab-EE</t>
-  </si>
-  <si>
     <t>22320-6</t>
   </si>
   <si>
@@ -3798,6 +3750,54 @@
   </si>
   <si>
     <t>lab-242</t>
+  </si>
+  <si>
+    <t>lab-243</t>
+  </si>
+  <si>
+    <t>lab-244</t>
+  </si>
+  <si>
+    <t>lab-245</t>
+  </si>
+  <si>
+    <t>lab-246</t>
+  </si>
+  <si>
+    <t>lab-247</t>
+  </si>
+  <si>
+    <t>lab-248</t>
+  </si>
+  <si>
+    <t>lab-249</t>
+  </si>
+  <si>
+    <t>lab-250</t>
+  </si>
+  <si>
+    <t>lab-251</t>
+  </si>
+  <si>
+    <t>lab-252</t>
+  </si>
+  <si>
+    <t>lab-253</t>
+  </si>
+  <si>
+    <t>lab-254</t>
+  </si>
+  <si>
+    <t>lab-255</t>
+  </si>
+  <si>
+    <t>lab-256</t>
+  </si>
+  <si>
+    <t>lab-257</t>
+  </si>
+  <si>
+    <t>lab-258</t>
   </si>
 </sst>
 </file>
@@ -3981,12 +3981,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4017,6 +4011,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4309,13 +4309,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -4348,7 +4348,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="78" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -4373,8 +4373,8 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>995</v>
+      <c r="A4" s="22" t="s">
+        <v>979</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>10</v>
@@ -4397,8 +4397,8 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
-        <v>996</v>
+      <c r="A5" s="22" t="s">
+        <v>980</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>14</v>
@@ -4421,8 +4421,8 @@
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>997</v>
+      <c r="A6" s="22" t="s">
+        <v>981</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>17</v>
@@ -4445,8 +4445,8 @@
       <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
-        <v>998</v>
+      <c r="A7" s="22" t="s">
+        <v>982</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>20</v>
@@ -4469,8 +4469,8 @@
       <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>999</v>
+      <c r="A8" s="22" t="s">
+        <v>983</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>23</v>
@@ -4493,8 +4493,8 @@
       <c r="L8" s="1"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>1000</v>
+      <c r="A9" s="22" t="s">
+        <v>984</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>26</v>
@@ -4517,8 +4517,8 @@
       <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>1001</v>
+      <c r="A10" s="22" t="s">
+        <v>985</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>29</v>
@@ -4541,8 +4541,8 @@
       <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
-        <v>1002</v>
+      <c r="A11" s="22" t="s">
+        <v>986</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>32</v>
@@ -4565,8 +4565,8 @@
       <c r="L11" s="1"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
-        <v>1003</v>
+      <c r="A12" s="22" t="s">
+        <v>987</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>35</v>
@@ -4589,8 +4589,8 @@
       <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>1004</v>
+      <c r="A13" s="22" t="s">
+        <v>988</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>38</v>
@@ -4613,8 +4613,8 @@
       <c r="L13" s="1"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
-        <v>1005</v>
+      <c r="A14" s="22" t="s">
+        <v>989</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>41</v>
@@ -4637,8 +4637,8 @@
       <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>1006</v>
+      <c r="A15" s="22" t="s">
+        <v>990</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>44</v>
@@ -4661,8 +4661,8 @@
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>1007</v>
+      <c r="A16" s="22" t="s">
+        <v>991</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>47</v>
@@ -4685,8 +4685,8 @@
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
-        <v>1008</v>
+      <c r="A17" s="22" t="s">
+        <v>992</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>50</v>
@@ -4709,8 +4709,8 @@
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
-        <v>1009</v>
+      <c r="A18" s="22" t="s">
+        <v>993</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>53</v>
@@ -4733,8 +4733,8 @@
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
-        <v>1010</v>
+      <c r="A19" s="22" t="s">
+        <v>994</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>56</v>
@@ -4757,8 +4757,8 @@
       <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
-        <v>1011</v>
+      <c r="A20" s="22" t="s">
+        <v>995</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>59</v>
@@ -4781,8 +4781,8 @@
       <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
-        <v>1012</v>
+      <c r="A21" s="22" t="s">
+        <v>996</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>62</v>
@@ -4805,8 +4805,8 @@
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
-        <v>1013</v>
+      <c r="A22" s="22" t="s">
+        <v>997</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>65</v>
@@ -4829,8 +4829,8 @@
       <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
-        <v>1014</v>
+      <c r="A23" s="22" t="s">
+        <v>998</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>68</v>
@@ -4853,8 +4853,8 @@
       <c r="L23" s="1"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
-        <v>1015</v>
+      <c r="A24" s="22" t="s">
+        <v>999</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>71</v>
@@ -4877,8 +4877,8 @@
       <c r="L24" s="1"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
-        <v>1016</v>
+      <c r="A25" s="22" t="s">
+        <v>1000</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>74</v>
@@ -4901,8 +4901,8 @@
       <c r="L25" s="1"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>1017</v>
+      <c r="A26" s="22" t="s">
+        <v>1001</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>77</v>
@@ -4925,8 +4925,8 @@
       <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
-        <v>1018</v>
+      <c r="A27" s="22" t="s">
+        <v>1002</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>80</v>
@@ -4949,8 +4949,8 @@
       <c r="L27" s="1"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="24" t="s">
-        <v>1019</v>
+      <c r="A28" s="22" t="s">
+        <v>1003</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>83</v>
@@ -4973,8 +4973,8 @@
       <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
-        <v>1020</v>
+      <c r="A29" s="22" t="s">
+        <v>1004</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>86</v>
@@ -4997,8 +4997,8 @@
       <c r="L29" s="1"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
-        <v>1021</v>
+      <c r="A30" s="22" t="s">
+        <v>1005</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>89</v>
@@ -5021,8 +5021,8 @@
       <c r="L30" s="1"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
-        <v>1022</v>
+      <c r="A31" s="23" t="s">
+        <v>1006</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>93</v>
@@ -5045,8 +5045,8 @@
       <c r="L31" s="1"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="24" t="s">
-        <v>1023</v>
+      <c r="A32" s="22" t="s">
+        <v>1007</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>97</v>
@@ -5069,8 +5069,8 @@
       <c r="L32" s="1"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
-        <v>1024</v>
+      <c r="A33" s="22" t="s">
+        <v>1008</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>101</v>
@@ -5093,8 +5093,8 @@
       <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
-        <v>1025</v>
+      <c r="A34" s="22" t="s">
+        <v>1009</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>105</v>
@@ -5117,8 +5117,8 @@
       <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
-        <v>1026</v>
+      <c r="A35" s="22" t="s">
+        <v>1010</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>109</v>
@@ -5141,8 +5141,8 @@
       <c r="L35" s="1"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
-        <v>1027</v>
+      <c r="A36" s="22" t="s">
+        <v>1011</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>113</v>
@@ -5165,8 +5165,8 @@
       <c r="L36" s="1"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
-        <v>1028</v>
+      <c r="A37" s="22" t="s">
+        <v>1012</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>117</v>
@@ -5189,8 +5189,8 @@
       <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
-        <v>1029</v>
+      <c r="A38" s="22" t="s">
+        <v>1013</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>121</v>
@@ -5213,8 +5213,8 @@
       <c r="L38" s="1"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
-        <v>1030</v>
+      <c r="A39" s="22" t="s">
+        <v>1014</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>125</v>
@@ -5237,8 +5237,8 @@
       <c r="L39" s="1"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
-        <v>1031</v>
+      <c r="A40" s="22" t="s">
+        <v>1015</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>129</v>
@@ -5261,8 +5261,8 @@
       <c r="L40" s="1"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="24" t="s">
-        <v>1032</v>
+      <c r="A41" s="22" t="s">
+        <v>1016</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>133</v>
@@ -5285,8 +5285,8 @@
       <c r="L41" s="1"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
-        <v>1033</v>
+      <c r="A42" s="22" t="s">
+        <v>1017</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>137</v>
@@ -5309,8 +5309,8 @@
       <c r="L42" s="1"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="24" t="s">
-        <v>1034</v>
+      <c r="A43" s="22" t="s">
+        <v>1018</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>141</v>
@@ -5333,8 +5333,8 @@
       <c r="L43" s="1"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
-        <v>1035</v>
+      <c r="A44" s="22" t="s">
+        <v>1019</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>145</v>
@@ -5357,8 +5357,8 @@
       <c r="L44" s="1"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="24" t="s">
-        <v>1036</v>
+      <c r="A45" s="22" t="s">
+        <v>1020</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>149</v>
@@ -5381,8 +5381,8 @@
       <c r="L45" s="1"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
-        <v>1037</v>
+      <c r="A46" s="13" t="s">
+        <v>1021</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>125</v>
@@ -5405,8 +5405,8 @@
       <c r="L46" s="1"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
-        <v>1038</v>
+      <c r="A47" s="22" t="s">
+        <v>1022</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>129</v>
@@ -5429,8 +5429,8 @@
       <c r="L47" s="1"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
-        <v>1039</v>
+      <c r="A48" s="22" t="s">
+        <v>1023</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>133</v>
@@ -5453,8 +5453,8 @@
       <c r="L48" s="1"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
-        <v>1040</v>
+      <c r="A49" s="22" t="s">
+        <v>1024</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>137</v>
@@ -5477,8 +5477,8 @@
       <c r="L49" s="1"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="24" t="s">
-        <v>1041</v>
+      <c r="A50" s="22" t="s">
+        <v>1025</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>141</v>
@@ -5501,8 +5501,8 @@
       <c r="L50" s="1"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="24" t="s">
-        <v>1042</v>
+      <c r="A51" s="22" t="s">
+        <v>1026</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>145</v>
@@ -5525,8 +5525,8 @@
       <c r="L51" s="1"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="24" t="s">
-        <v>1043</v>
+      <c r="A52" s="22" t="s">
+        <v>1027</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>149</v>
@@ -5549,8 +5549,8 @@
       <c r="L52" s="1"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
-        <v>1044</v>
+      <c r="A53" s="13" t="s">
+        <v>1028</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
@@ -5571,8 +5571,8 @@
       <c r="L53" s="1"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
-        <v>1043</v>
+      <c r="A54" s="22" t="s">
+        <v>1027</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>158</v>
@@ -5595,8 +5595,8 @@
       <c r="L54" s="1"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="24" t="s">
-        <v>1045</v>
+      <c r="A55" s="22" t="s">
+        <v>1029</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>162</v>
@@ -5619,8 +5619,8 @@
       <c r="L55" s="1"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="24" t="s">
-        <v>1046</v>
+      <c r="A56" s="22" t="s">
+        <v>1030</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>166</v>
@@ -5643,8 +5643,8 @@
       <c r="L56" s="1"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="24" t="s">
-        <v>1047</v>
+      <c r="A57" s="22" t="s">
+        <v>1031</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>170</v>
@@ -5667,8 +5667,8 @@
       <c r="L57" s="1"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="24" t="s">
-        <v>1048</v>
+      <c r="A58" s="22" t="s">
+        <v>1032</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>174</v>
@@ -5691,8 +5691,8 @@
       <c r="L58" s="1"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="24" t="s">
-        <v>1049</v>
+      <c r="A59" s="22" t="s">
+        <v>1033</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>178</v>
@@ -5715,8 +5715,8 @@
       <c r="L59" s="1"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="24" t="s">
-        <v>1050</v>
+      <c r="A60" s="22" t="s">
+        <v>1034</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>182</v>
@@ -5739,8 +5739,8 @@
       <c r="L60" s="1"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
-        <v>1051</v>
+      <c r="A61" s="22" t="s">
+        <v>1035</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>186</v>
@@ -5763,8 +5763,8 @@
       <c r="L61" s="1"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="24" t="s">
-        <v>1052</v>
+      <c r="A62" s="22" t="s">
+        <v>1036</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>190</v>
@@ -5787,8 +5787,8 @@
       <c r="L62" s="1"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="24" t="s">
-        <v>1053</v>
+      <c r="A63" s="22" t="s">
+        <v>1037</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>194</v>
@@ -5811,8 +5811,8 @@
       <c r="L63" s="1"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="24" t="s">
-        <v>1054</v>
+      <c r="A64" s="22" t="s">
+        <v>1038</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>198</v>
@@ -5835,8 +5835,8 @@
       <c r="L64" s="1"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="24" t="s">
-        <v>1055</v>
+      <c r="A65" s="22" t="s">
+        <v>1039</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>202</v>
@@ -5859,8 +5859,8 @@
       <c r="L65" s="1"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="24" t="s">
-        <v>1056</v>
+      <c r="A66" s="22" t="s">
+        <v>1040</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>206</v>
@@ -5883,8 +5883,8 @@
       <c r="L66" s="1"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="24" t="s">
-        <v>1057</v>
+      <c r="A67" s="22" t="s">
+        <v>1041</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>208</v>
@@ -5907,8 +5907,8 @@
       <c r="L67" s="1"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="24" t="s">
-        <v>1058</v>
+      <c r="A68" s="22" t="s">
+        <v>1042</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>212</v>
@@ -5931,8 +5931,8 @@
       <c r="L68" s="1"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="24" t="s">
-        <v>1059</v>
+      <c r="A69" s="22" t="s">
+        <v>1043</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>216</v>
@@ -5955,8 +5955,8 @@
       <c r="L69" s="1"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="24" t="s">
-        <v>1060</v>
+      <c r="A70" s="22" t="s">
+        <v>1044</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>220</v>
@@ -5979,8 +5979,8 @@
       <c r="L70" s="1"/>
     </row>
     <row r="71" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="24" t="s">
-        <v>1061</v>
+      <c r="A71" s="22" t="s">
+        <v>1045</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>224</v>
@@ -6003,8 +6003,8 @@
       <c r="L71" s="1"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="24" t="s">
-        <v>1062</v>
+      <c r="A72" s="22" t="s">
+        <v>1046</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>228</v>
@@ -6027,8 +6027,8 @@
       <c r="L72" s="1"/>
     </row>
     <row r="73" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A73" s="24" t="s">
-        <v>1063</v>
+      <c r="A73" s="22" t="s">
+        <v>1047</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>232</v>
@@ -6051,8 +6051,8 @@
       <c r="L73" s="1"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="24" t="s">
-        <v>1064</v>
+      <c r="A74" s="22" t="s">
+        <v>1048</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>236</v>
@@ -6075,8 +6075,8 @@
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A75" s="24" t="s">
-        <v>1065</v>
+      <c r="A75" s="22" t="s">
+        <v>1049</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>240</v>
@@ -6099,8 +6099,8 @@
       <c r="L75" s="1"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="15" t="s">
-        <v>1066</v>
+      <c r="A76" s="13" t="s">
+        <v>1050</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>244</v>
@@ -6123,8 +6123,8 @@
       <c r="L76" s="1"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="24" t="s">
-        <v>1067</v>
+      <c r="A77" s="22" t="s">
+        <v>1051</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>248</v>
@@ -6147,8 +6147,8 @@
       <c r="L77" s="1"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="24" t="s">
-        <v>1068</v>
+      <c r="A78" s="22" t="s">
+        <v>1052</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>252</v>
@@ -6171,8 +6171,8 @@
       <c r="L78" s="1"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="24" t="s">
-        <v>1069</v>
+      <c r="A79" s="22" t="s">
+        <v>1053</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>256</v>
@@ -6195,8 +6195,8 @@
       <c r="L79" s="1"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
-        <v>1070</v>
+      <c r="A80" s="22" t="s">
+        <v>1054</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>260</v>
@@ -6219,8 +6219,8 @@
       <c r="L80" s="1"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="24" t="s">
-        <v>1071</v>
+      <c r="A81" s="22" t="s">
+        <v>1055</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>264</v>
@@ -6243,8 +6243,8 @@
       <c r="L81" s="1"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="24" t="s">
-        <v>1072</v>
+      <c r="A82" s="22" t="s">
+        <v>1056</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>268</v>
@@ -6267,8 +6267,8 @@
       <c r="L82" s="1"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="24" t="s">
-        <v>1073</v>
+      <c r="A83" s="22" t="s">
+        <v>1057</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>272</v>
@@ -6291,8 +6291,8 @@
       <c r="L83" s="1"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="24" t="s">
-        <v>1074</v>
+      <c r="A84" s="22" t="s">
+        <v>1058</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>276</v>
@@ -6315,8 +6315,8 @@
       <c r="L84" s="1"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="24" t="s">
-        <v>1075</v>
+      <c r="A85" s="22" t="s">
+        <v>1059</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>280</v>
@@ -6339,8 +6339,8 @@
       <c r="L85" s="1"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="24" t="s">
-        <v>1076</v>
+      <c r="A86" s="22" t="s">
+        <v>1060</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>284</v>
@@ -6363,8 +6363,8 @@
       <c r="L86" s="1"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="24" t="s">
-        <v>1077</v>
+      <c r="A87" s="22" t="s">
+        <v>1061</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>288</v>
@@ -6387,8 +6387,8 @@
       <c r="L87" s="1"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="24" t="s">
-        <v>1078</v>
+      <c r="A88" s="22" t="s">
+        <v>1062</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>292</v>
@@ -6411,8 +6411,8 @@
       <c r="L88" s="1"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="14" t="s">
-        <v>1079</v>
+      <c r="A89" s="12" t="s">
+        <v>1063</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>296</v>
@@ -6435,8 +6435,8 @@
       <c r="L89" s="1"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="24" t="s">
-        <v>1080</v>
+      <c r="A90" s="22" t="s">
+        <v>1064</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>300</v>
@@ -6459,8 +6459,8 @@
       <c r="L90" s="1"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="24" t="s">
-        <v>1081</v>
+      <c r="A91" s="22" t="s">
+        <v>1065</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>304</v>
@@ -6483,8 +6483,8 @@
       <c r="L91" s="1"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="24" t="s">
-        <v>1082</v>
+      <c r="A92" s="22" t="s">
+        <v>1066</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>308</v>
@@ -6507,8 +6507,8 @@
       <c r="L92" s="1"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="24" t="s">
-        <v>1083</v>
+      <c r="A93" s="22" t="s">
+        <v>1067</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>129</v>
@@ -6531,8 +6531,8 @@
       <c r="L93" s="1"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="24" t="s">
-        <v>1084</v>
+      <c r="A94" s="22" t="s">
+        <v>1068</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>313</v>
@@ -6555,8 +6555,8 @@
       <c r="L94" s="1"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="24" t="s">
-        <v>1085</v>
+      <c r="A95" s="22" t="s">
+        <v>1069</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>137</v>
@@ -6579,8 +6579,8 @@
       <c r="L95" s="1"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="24" t="s">
-        <v>1086</v>
+      <c r="A96" s="22" t="s">
+        <v>1070</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>320</v>
@@ -6603,8 +6603,8 @@
       <c r="L96" s="1"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="24" t="s">
-        <v>1087</v>
+      <c r="A97" s="22" t="s">
+        <v>1071</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>324</v>
@@ -6627,8 +6627,8 @@
       <c r="L97" s="1"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
-        <v>1088</v>
+      <c r="A98" s="22" t="s">
+        <v>1072</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>328</v>
@@ -6651,8 +6651,8 @@
       <c r="L98" s="1"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="24" t="s">
-        <v>1089</v>
+      <c r="A99" s="22" t="s">
+        <v>1073</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>332</v>
@@ -6675,8 +6675,8 @@
       <c r="L99" s="1"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="24" t="s">
-        <v>1090</v>
+      <c r="A100" s="22" t="s">
+        <v>1074</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>336</v>
@@ -6699,8 +6699,8 @@
       <c r="L100" s="1"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="24" t="s">
-        <v>1091</v>
+      <c r="A101" s="22" t="s">
+        <v>1075</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>340</v>
@@ -6723,8 +6723,8 @@
       <c r="L101" s="1"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="24" t="s">
-        <v>1092</v>
+      <c r="A102" s="22" t="s">
+        <v>1076</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>344</v>
@@ -6747,8 +6747,8 @@
       <c r="L102" s="1"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="24" t="s">
-        <v>1093</v>
+      <c r="A103" s="22" t="s">
+        <v>1077</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>346</v>
@@ -6771,8 +6771,8 @@
       <c r="L103" s="1"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="24" t="s">
-        <v>1094</v>
+      <c r="A104" s="22" t="s">
+        <v>1078</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>350</v>
@@ -6795,8 +6795,8 @@
       <c r="L104" s="1"/>
     </row>
     <row r="105" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A105" s="15" t="s">
-        <v>1095</v>
+      <c r="A105" s="13" t="s">
+        <v>1079</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>354</v>
@@ -6819,8 +6819,8 @@
       <c r="L105" s="1"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="24" t="s">
-        <v>1096</v>
+      <c r="A106" s="22" t="s">
+        <v>1080</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>358</v>
@@ -6843,8 +6843,8 @@
       <c r="L106" s="1"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="24" t="s">
-        <v>1097</v>
+      <c r="A107" s="22" t="s">
+        <v>1081</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>362</v>
@@ -6867,8 +6867,8 @@
       <c r="L107" s="1"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="24" t="s">
-        <v>1098</v>
+      <c r="A108" s="22" t="s">
+        <v>1082</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>366</v>
@@ -6891,8 +6891,8 @@
       <c r="L108" s="1"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="24" t="s">
-        <v>1099</v>
+      <c r="A109" s="22" t="s">
+        <v>1083</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>370</v>
@@ -6915,8 +6915,8 @@
       <c r="L109" s="1"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="24" t="s">
-        <v>1100</v>
+      <c r="A110" s="22" t="s">
+        <v>1084</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>374</v>
@@ -6939,8 +6939,8 @@
       <c r="L110" s="1"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="24" t="s">
-        <v>1101</v>
+      <c r="A111" s="22" t="s">
+        <v>1085</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>377</v>
@@ -6963,8 +6963,8 @@
       <c r="L111" s="1"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="24" t="s">
-        <v>1102</v>
+      <c r="A112" s="22" t="s">
+        <v>1086</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>381</v>
@@ -6987,8 +6987,8 @@
       <c r="L112" s="1"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="24" t="s">
-        <v>1103</v>
+      <c r="A113" s="22" t="s">
+        <v>1087</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>385</v>
@@ -7011,8 +7011,8 @@
       <c r="L113" s="1"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="24" t="s">
-        <v>1104</v>
+      <c r="A114" s="22" t="s">
+        <v>1088</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>389</v>
@@ -7035,8 +7035,8 @@
       <c r="L114" s="1"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
-        <v>1105</v>
+      <c r="A115" s="22" t="s">
+        <v>1089</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>393</v>
@@ -7059,8 +7059,8 @@
       <c r="L115" s="1"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="24" t="s">
-        <v>1106</v>
+      <c r="A116" s="22" t="s">
+        <v>1090</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>397</v>
@@ -7083,8 +7083,8 @@
       <c r="L116" s="1"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="24" t="s">
-        <v>1107</v>
+      <c r="A117" s="22" t="s">
+        <v>1091</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>401</v>
@@ -7107,8 +7107,8 @@
       <c r="L117" s="1"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="24" t="s">
-        <v>1108</v>
+      <c r="A118" s="22" t="s">
+        <v>1092</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>405</v>
@@ -7131,8 +7131,8 @@
       <c r="L118" s="1"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="24" t="s">
-        <v>1109</v>
+      <c r="A119" s="22" t="s">
+        <v>1093</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>409</v>
@@ -7155,8 +7155,8 @@
       <c r="L119" s="1"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="24" t="s">
-        <v>1110</v>
+      <c r="A120" s="22" t="s">
+        <v>1094</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>413</v>
@@ -7179,8 +7179,8 @@
       <c r="L120" s="1"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="24" t="s">
-        <v>1111</v>
+      <c r="A121" s="22" t="s">
+        <v>1095</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>417</v>
@@ -7203,8 +7203,8 @@
       <c r="L121" s="1"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="24" t="s">
-        <v>1112</v>
+      <c r="A122" s="22" t="s">
+        <v>1096</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>421</v>
@@ -7227,8 +7227,8 @@
       <c r="L122" s="1"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="24" t="s">
-        <v>1113</v>
+      <c r="A123" s="22" t="s">
+        <v>1097</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>425</v>
@@ -7251,8 +7251,8 @@
       <c r="L123" s="1"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="24" t="s">
-        <v>1114</v>
+      <c r="A124" s="22" t="s">
+        <v>1098</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>429</v>
@@ -7275,8 +7275,8 @@
       <c r="L124" s="1"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="24" t="s">
-        <v>1115</v>
+      <c r="A125" s="22" t="s">
+        <v>1099</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>433</v>
@@ -7299,8 +7299,8 @@
       <c r="L125" s="1"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="24" t="s">
-        <v>1116</v>
+      <c r="A126" s="22" t="s">
+        <v>1100</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>437</v>
@@ -7323,8 +7323,8 @@
       <c r="L126" s="1"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="24" t="s">
-        <v>1117</v>
+      <c r="A127" s="22" t="s">
+        <v>1101</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>441</v>
@@ -7347,8 +7347,8 @@
       <c r="L127" s="1"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="15" t="s">
-        <v>1118</v>
+      <c r="A128" s="13" t="s">
+        <v>1102</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>445</v>
@@ -7371,8 +7371,8 @@
       <c r="L128" s="1"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A129" s="24" t="s">
-        <v>1119</v>
+      <c r="A129" s="22" t="s">
+        <v>1103</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>449</v>
@@ -7395,8 +7395,8 @@
       <c r="L129" s="1"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" s="24" t="s">
-        <v>1120</v>
+      <c r="A130" s="22" t="s">
+        <v>1104</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>453</v>
@@ -7419,8 +7419,8 @@
       <c r="L130" s="1"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" s="24" t="s">
-        <v>1121</v>
+      <c r="A131" s="22" t="s">
+        <v>1105</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>457</v>
@@ -7443,8 +7443,8 @@
       <c r="L131" s="1"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
-        <v>1122</v>
+      <c r="A132" s="22" t="s">
+        <v>1106</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>461</v>
@@ -7467,8 +7467,8 @@
       <c r="L132" s="1"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A133" s="24" t="s">
-        <v>1123</v>
+      <c r="A133" s="22" t="s">
+        <v>1107</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>465</v>
@@ -7491,8 +7491,8 @@
       <c r="L133" s="1"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A134" s="24" t="s">
-        <v>1124</v>
+      <c r="A134" s="22" t="s">
+        <v>1108</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>469</v>
@@ -7515,8 +7515,8 @@
       <c r="L134" s="1"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A135" s="24" t="s">
-        <v>1125</v>
+      <c r="A135" s="22" t="s">
+        <v>1109</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>473</v>
@@ -7539,8 +7539,8 @@
       <c r="L135" s="1"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="24" t="s">
-        <v>1126</v>
+      <c r="A136" s="22" t="s">
+        <v>1110</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>477</v>
@@ -7563,8 +7563,8 @@
       <c r="L136" s="1"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A137" s="24" t="s">
-        <v>1127</v>
+      <c r="A137" s="22" t="s">
+        <v>1111</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>481</v>
@@ -7587,8 +7587,8 @@
       <c r="L137" s="1"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" s="24" t="s">
-        <v>1128</v>
+      <c r="A138" s="22" t="s">
+        <v>1112</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>485</v>
@@ -7611,8 +7611,8 @@
       <c r="L138" s="1"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" s="24" t="s">
-        <v>1129</v>
+      <c r="A139" s="22" t="s">
+        <v>1113</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>489</v>
@@ -7635,8 +7635,8 @@
       <c r="L139" s="1"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" s="15" t="s">
-        <v>1130</v>
+      <c r="A140" s="13" t="s">
+        <v>1114</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>493</v>
@@ -7659,8 +7659,8 @@
       <c r="L140" s="1"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A141" s="24" t="s">
-        <v>1131</v>
+      <c r="A141" s="22" t="s">
+        <v>1115</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>497</v>
@@ -7683,8 +7683,8 @@
       <c r="L141" s="1"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A142" s="24" t="s">
-        <v>1132</v>
+      <c r="A142" s="22" t="s">
+        <v>1116</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>501</v>
@@ -7707,8 +7707,8 @@
       <c r="L142" s="1"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" s="24" t="s">
-        <v>1133</v>
+      <c r="A143" s="22" t="s">
+        <v>1117</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>504</v>
@@ -7731,8 +7731,8 @@
       <c r="L143" s="1"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A144" s="24" t="s">
-        <v>1134</v>
+      <c r="A144" s="22" t="s">
+        <v>1118</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>508</v>
@@ -7755,8 +7755,8 @@
       <c r="L144" s="1"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A145" s="24" t="s">
-        <v>1135</v>
+      <c r="A145" s="22" t="s">
+        <v>1119</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>512</v>
@@ -7779,8 +7779,8 @@
       <c r="L145" s="1"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" s="24" t="s">
-        <v>1136</v>
+      <c r="A146" s="22" t="s">
+        <v>1120</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>516</v>
@@ -7803,8 +7803,8 @@
       <c r="L146" s="1"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" s="24" t="s">
-        <v>1137</v>
+      <c r="A147" s="22" t="s">
+        <v>1121</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>520</v>
@@ -7827,8 +7827,8 @@
       <c r="L147" s="1"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A148" s="24" t="s">
-        <v>1138</v>
+      <c r="A148" s="22" t="s">
+        <v>1122</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>524</v>
@@ -7851,8 +7851,8 @@
       <c r="L148" s="1"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
-        <v>1139</v>
+      <c r="A149" s="22" t="s">
+        <v>1123</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>528</v>
@@ -7875,8 +7875,8 @@
       <c r="L149" s="1"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A150" s="24" t="s">
-        <v>1140</v>
+      <c r="A150" s="22" t="s">
+        <v>1124</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>532</v>
@@ -7899,8 +7899,8 @@
       <c r="L150" s="1"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A151" s="24" t="s">
-        <v>1141</v>
+      <c r="A151" s="22" t="s">
+        <v>1125</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>536</v>
@@ -7923,8 +7923,8 @@
       <c r="L151" s="1"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A152" s="24" t="s">
-        <v>1142</v>
+      <c r="A152" s="22" t="s">
+        <v>1126</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>540</v>
@@ -7947,8 +7947,8 @@
       <c r="L152" s="1"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" s="24" t="s">
-        <v>1143</v>
+      <c r="A153" s="22" t="s">
+        <v>1127</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>544</v>
@@ -7971,8 +7971,8 @@
       <c r="L153" s="1"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A154" s="24" t="s">
-        <v>1144</v>
+      <c r="A154" s="22" t="s">
+        <v>1128</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>548</v>
@@ -7995,8 +7995,8 @@
       <c r="L154" s="1"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" s="24" t="s">
-        <v>1145</v>
+      <c r="A155" s="22" t="s">
+        <v>1129</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>552</v>
@@ -8019,8 +8019,8 @@
       <c r="L155" s="1"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A156" s="24" t="s">
-        <v>1146</v>
+      <c r="A156" s="22" t="s">
+        <v>1130</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>554</v>
@@ -8043,8 +8043,8 @@
       <c r="L156" s="1"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="24" t="s">
-        <v>1147</v>
+      <c r="A157" s="22" t="s">
+        <v>1131</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>558</v>
@@ -8067,8 +8067,8 @@
       <c r="L157" s="1"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A158" s="24" t="s">
-        <v>1148</v>
+      <c r="A158" s="22" t="s">
+        <v>1132</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>562</v>
@@ -8091,8 +8091,8 @@
       <c r="L158" s="1"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="24" t="s">
-        <v>1149</v>
+      <c r="A159" s="22" t="s">
+        <v>1133</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>566</v>
@@ -8115,8 +8115,8 @@
       <c r="L159" s="1"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A160" s="15" t="s">
-        <v>1150</v>
+      <c r="A160" s="13" t="s">
+        <v>1134</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>570</v>
@@ -8139,8 +8139,8 @@
       <c r="L160" s="1"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="24" t="s">
-        <v>1151</v>
+      <c r="A161" s="22" t="s">
+        <v>1135</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>574</v>
@@ -8163,8 +8163,8 @@
       <c r="L161" s="1"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="24" t="s">
-        <v>1152</v>
+      <c r="A162" s="22" t="s">
+        <v>1136</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>504</v>
@@ -8187,8 +8187,8 @@
       <c r="L162" s="1"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="24" t="s">
-        <v>1153</v>
+      <c r="A163" s="22" t="s">
+        <v>1137</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>578</v>
@@ -8211,8 +8211,8 @@
       <c r="L163" s="1"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="24" t="s">
-        <v>1154</v>
+      <c r="A164" s="22" t="s">
+        <v>1138</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>570</v>
@@ -8235,8 +8235,8 @@
       <c r="L164" s="1"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="24" t="s">
-        <v>1155</v>
+      <c r="A165" s="22" t="s">
+        <v>1139</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>583</v>
@@ -8259,8 +8259,8 @@
       <c r="L165" s="1"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="24" t="s">
-        <v>1156</v>
+      <c r="A166" s="22" t="s">
+        <v>1140</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>587</v>
@@ -8283,8 +8283,8 @@
       <c r="L166" s="1"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
-        <v>1157</v>
+      <c r="A167" s="22" t="s">
+        <v>1141</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>591</v>
@@ -8307,8 +8307,8 @@
       <c r="L167" s="1"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="24" t="s">
-        <v>1158</v>
+      <c r="A168" s="22" t="s">
+        <v>1142</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>593</v>
@@ -8331,8 +8331,8 @@
       <c r="L168" s="1"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A169" s="24" t="s">
-        <v>1159</v>
+      <c r="A169" s="22" t="s">
+        <v>1143</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>597</v>
@@ -8355,8 +8355,8 @@
       <c r="L169" s="1"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A170" s="24" t="s">
-        <v>1160</v>
+      <c r="A170" s="22" t="s">
+        <v>1144</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>599</v>
@@ -8379,8 +8379,8 @@
       <c r="L170" s="1"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" s="24" t="s">
-        <v>1161</v>
+      <c r="A171" s="22" t="s">
+        <v>1145</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>601</v>
@@ -8403,8 +8403,8 @@
       <c r="L171" s="1"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A172" s="24" t="s">
-        <v>1162</v>
+      <c r="A172" s="22" t="s">
+        <v>1146</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>605</v>
@@ -8427,8 +8427,8 @@
       <c r="L172" s="1"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="24" t="s">
-        <v>1163</v>
+      <c r="A173" s="22" t="s">
+        <v>1147</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>609</v>
@@ -8451,8 +8451,8 @@
       <c r="L173" s="1"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A174" s="24" t="s">
-        <v>1164</v>
+      <c r="A174" s="22" t="s">
+        <v>1148</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>613</v>
@@ -8475,8 +8475,8 @@
       <c r="L174" s="1"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175" s="24" t="s">
-        <v>1165</v>
+      <c r="A175" s="22" t="s">
+        <v>1149</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>617</v>
@@ -8499,8 +8499,8 @@
       <c r="L175" s="1"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176" s="24" t="s">
-        <v>1166</v>
+      <c r="A176" s="22" t="s">
+        <v>1150</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>621</v>
@@ -8523,8 +8523,8 @@
       <c r="L176" s="1"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" s="24" t="s">
-        <v>1167</v>
+      <c r="A177" s="22" t="s">
+        <v>1151</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>623</v>
@@ -8547,8 +8547,8 @@
       <c r="L177" s="1"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="24" t="s">
-        <v>1168</v>
+      <c r="A178" s="22" t="s">
+        <v>1152</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>627</v>
@@ -8571,8 +8571,8 @@
       <c r="L178" s="1"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="24" t="s">
-        <v>1169</v>
+      <c r="A179" s="22" t="s">
+        <v>1153</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>631</v>
@@ -8595,8 +8595,8 @@
       <c r="L179" s="1"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" s="24" t="s">
-        <v>1170</v>
+      <c r="A180" s="22" t="s">
+        <v>1154</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>635</v>
@@ -8619,8 +8619,8 @@
       <c r="L180" s="1"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" s="15" t="s">
-        <v>1171</v>
+      <c r="A181" s="13" t="s">
+        <v>1155</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>220</v>
@@ -8643,8 +8643,8 @@
       <c r="L181" s="1"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" s="24" t="s">
-        <v>1172</v>
+      <c r="A182" s="22" t="s">
+        <v>1156</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>642</v>
@@ -8667,8 +8667,8 @@
       <c r="L182" s="1"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" s="24" t="s">
-        <v>1173</v>
+      <c r="A183" s="22" t="s">
+        <v>1157</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>644</v>
@@ -8691,8 +8691,8 @@
       <c r="L183" s="1"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A184" s="24" t="s">
-        <v>1174</v>
+      <c r="A184" s="22" t="s">
+        <v>1158</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>646</v>
@@ -8715,8 +8715,8 @@
       <c r="L184" s="1"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A185" s="24" t="s">
-        <v>1175</v>
+      <c r="A185" s="22" t="s">
+        <v>1159</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>649</v>
@@ -8739,8 +8739,8 @@
       <c r="L185" s="1"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A186" s="24" t="s">
-        <v>1176</v>
+      <c r="A186" s="22" t="s">
+        <v>1160</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>651</v>
@@ -8763,8 +8763,8 @@
       <c r="L186" s="1"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A187" s="24" t="s">
-        <v>1177</v>
+      <c r="A187" s="22" t="s">
+        <v>1161</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>653</v>
@@ -8787,8 +8787,8 @@
       <c r="L187" s="1"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A188" s="24" t="s">
-        <v>1178</v>
+      <c r="A188" s="22" t="s">
+        <v>1162</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>655</v>
@@ -8811,8 +8811,8 @@
       <c r="L188" s="1"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A189" s="24" t="s">
-        <v>1179</v>
+      <c r="A189" s="22" t="s">
+        <v>1163</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>657</v>
@@ -8835,8 +8835,8 @@
       <c r="L189" s="1"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A190" s="24" t="s">
-        <v>1180</v>
+      <c r="A190" s="22" t="s">
+        <v>1164</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>661</v>
@@ -8859,8 +8859,8 @@
       <c r="L190" s="1"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" s="24" t="s">
-        <v>1181</v>
+      <c r="A191" s="22" t="s">
+        <v>1165</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>663</v>
@@ -8883,8 +8883,8 @@
       <c r="L191" s="1"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A192" s="24" t="s">
-        <v>1182</v>
+      <c r="A192" s="22" t="s">
+        <v>1166</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>667</v>
@@ -8907,8 +8907,8 @@
       <c r="L192" s="1"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A193" s="24" t="s">
-        <v>1183</v>
+      <c r="A193" s="22" t="s">
+        <v>1167</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>671</v>
@@ -8931,8 +8931,8 @@
       <c r="L193" s="1"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A194" s="24" t="s">
-        <v>1184</v>
+      <c r="A194" s="22" t="s">
+        <v>1168</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>673</v>
@@ -8955,8 +8955,8 @@
       <c r="L194" s="1"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A195" s="24" t="s">
-        <v>1185</v>
+      <c r="A195" s="22" t="s">
+        <v>1169</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>675</v>
@@ -8979,8 +8979,8 @@
       <c r="L195" s="1"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A196" s="24" t="s">
-        <v>1186</v>
+      <c r="A196" s="22" t="s">
+        <v>1170</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>677</v>
@@ -9003,8 +9003,8 @@
       <c r="L196" s="1"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="15" t="s">
-        <v>1187</v>
+      <c r="A197" s="13" t="s">
+        <v>1171</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>679</v>
@@ -9027,8 +9027,8 @@
       <c r="L197" s="1"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A198" s="24" t="s">
-        <v>1188</v>
+      <c r="A198" s="22" t="s">
+        <v>1172</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>683</v>
@@ -9051,8 +9051,8 @@
       <c r="L198" s="1"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A199" s="24" t="s">
-        <v>1189</v>
+      <c r="A199" s="22" t="s">
+        <v>1173</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>687</v>
@@ -9075,8 +9075,8 @@
       <c r="L199" s="1"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A200" s="24" t="s">
-        <v>1190</v>
+      <c r="A200" s="22" t="s">
+        <v>1174</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>691</v>
@@ -9099,8 +9099,8 @@
       <c r="L200" s="1"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="24" t="s">
-        <v>1191</v>
+      <c r="A201" s="22" t="s">
+        <v>1175</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>695</v>
@@ -9123,8 +9123,8 @@
       <c r="L201" s="1"/>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A202" s="24" t="s">
-        <v>1192</v>
+      <c r="A202" s="22" t="s">
+        <v>1176</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>699</v>
@@ -9147,8 +9147,8 @@
       <c r="L202" s="1"/>
     </row>
     <row r="203" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A203" s="15" t="s">
-        <v>1193</v>
+      <c r="A203" s="13" t="s">
+        <v>1177</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>703</v>
@@ -9171,8 +9171,8 @@
       <c r="L203" s="1"/>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A204" s="24" t="s">
-        <v>1194</v>
+      <c r="A204" s="22" t="s">
+        <v>1178</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>707</v>
@@ -9195,8 +9195,8 @@
       <c r="L204" s="1"/>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A205" s="24" t="s">
-        <v>1195</v>
+      <c r="A205" s="22" t="s">
+        <v>1179</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>709</v>
@@ -9219,8 +9219,8 @@
       <c r="L205" s="1"/>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A206" s="24" t="s">
-        <v>1196</v>
+      <c r="A206" s="22" t="s">
+        <v>1180</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>713</v>
@@ -9243,8 +9243,8 @@
       <c r="L206" s="1"/>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A207" s="24" t="s">
-        <v>1197</v>
+      <c r="A207" s="22" t="s">
+        <v>1181</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>717</v>
@@ -9267,8 +9267,8 @@
       <c r="L207" s="1"/>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A208" s="24" t="s">
-        <v>1198</v>
+      <c r="A208" s="22" t="s">
+        <v>1182</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>721</v>
@@ -9291,8 +9291,8 @@
       <c r="L208" s="1"/>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A209" s="24" t="s">
-        <v>1199</v>
+      <c r="A209" s="22" t="s">
+        <v>1183</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>724</v>
@@ -9315,8 +9315,8 @@
       <c r="L209" s="1"/>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A210" s="24" t="s">
-        <v>1200</v>
+      <c r="A210" s="22" t="s">
+        <v>1184</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>728</v>
@@ -9339,8 +9339,8 @@
       <c r="L210" s="1"/>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A211" s="24" t="s">
-        <v>1201</v>
+      <c r="A211" s="22" t="s">
+        <v>1185</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>732</v>
@@ -9363,8 +9363,8 @@
       <c r="L211" s="1"/>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A212" s="24" t="s">
-        <v>1202</v>
+      <c r="A212" s="22" t="s">
+        <v>1186</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>734</v>
@@ -9387,8 +9387,8 @@
       <c r="L212" s="1"/>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A213" s="24" t="s">
-        <v>1203</v>
+      <c r="A213" s="22" t="s">
+        <v>1187</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>738</v>
@@ -9411,8 +9411,8 @@
       <c r="L213" s="1"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A214" s="24" t="s">
-        <v>1204</v>
+      <c r="A214" s="22" t="s">
+        <v>1188</v>
       </c>
       <c r="B214" s="6" t="s">
         <v>740</v>
@@ -9435,8 +9435,8 @@
       <c r="L214" s="1"/>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A215" s="24" t="s">
-        <v>1205</v>
+      <c r="A215" s="22" t="s">
+        <v>1189</v>
       </c>
       <c r="B215" s="6" t="s">
         <v>744</v>
@@ -9459,8 +9459,8 @@
       <c r="L215" s="1"/>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A216" s="24" t="s">
-        <v>1206</v>
+      <c r="A216" s="22" t="s">
+        <v>1190</v>
       </c>
       <c r="B216" s="6" t="s">
         <v>748</v>
@@ -9483,8 +9483,8 @@
       <c r="L216" s="1"/>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A217" s="24" t="s">
-        <v>1207</v>
+      <c r="A217" s="22" t="s">
+        <v>1191</v>
       </c>
       <c r="B217" s="6" t="s">
         <v>752</v>
@@ -9507,8 +9507,8 @@
       <c r="L217" s="1"/>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A218" s="24" t="s">
-        <v>1208</v>
+      <c r="A218" s="22" t="s">
+        <v>1192</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>756</v>
@@ -9531,8 +9531,8 @@
       <c r="L218" s="1"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A219" s="24" t="s">
-        <v>1209</v>
+      <c r="A219" s="22" t="s">
+        <v>1193</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>760</v>
@@ -9555,8 +9555,8 @@
       <c r="L219" s="1"/>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A220" s="24" t="s">
-        <v>1210</v>
+      <c r="A220" s="22" t="s">
+        <v>1194</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>764</v>
@@ -9579,8 +9579,8 @@
       <c r="L220" s="1"/>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A221" s="24" t="s">
-        <v>1211</v>
+      <c r="A221" s="22" t="s">
+        <v>1195</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>766</v>
@@ -9603,8 +9603,8 @@
       <c r="L221" s="1"/>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A222" s="14" t="s">
-        <v>1212</v>
+      <c r="A222" s="12" t="s">
+        <v>1196</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>768</v>
@@ -9627,8 +9627,8 @@
       <c r="L222" s="1"/>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A223" s="24" t="s">
-        <v>1213</v>
+      <c r="A223" s="22" t="s">
+        <v>1197</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>772</v>
@@ -9651,8 +9651,8 @@
       <c r="L223" s="1"/>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A224" s="24" t="s">
-        <v>1214</v>
+      <c r="A224" s="22" t="s">
+        <v>1198</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>776</v>
@@ -9675,8 +9675,8 @@
       <c r="L224" s="1"/>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A225" s="24" t="s">
-        <v>1215</v>
+      <c r="A225" s="22" t="s">
+        <v>1199</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>780</v>
@@ -9699,8 +9699,8 @@
       <c r="L225" s="1"/>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A226" s="24" t="s">
-        <v>1216</v>
+      <c r="A226" s="22" t="s">
+        <v>1200</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>784</v>
@@ -9723,8 +9723,8 @@
       <c r="L226" s="1"/>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A227" s="24" t="s">
-        <v>1217</v>
+      <c r="A227" s="22" t="s">
+        <v>1201</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>788</v>
@@ -9747,8 +9747,8 @@
       <c r="L227" s="1"/>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A228" s="24" t="s">
-        <v>1218</v>
+      <c r="A228" s="22" t="s">
+        <v>1202</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>792</v>
@@ -9771,8 +9771,8 @@
       <c r="L228" s="1"/>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A229" s="24" t="s">
-        <v>1219</v>
+      <c r="A229" s="22" t="s">
+        <v>1203</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>796</v>
@@ -9795,8 +9795,8 @@
       <c r="L229" s="1"/>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A230" s="24" t="s">
-        <v>1220</v>
+      <c r="A230" s="22" t="s">
+        <v>1204</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>800</v>
@@ -9819,8 +9819,8 @@
       <c r="L230" s="1"/>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A231" s="24" t="s">
-        <v>1221</v>
+      <c r="A231" s="22" t="s">
+        <v>1205</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>804</v>
@@ -9843,8 +9843,8 @@
       <c r="L231" s="1"/>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A232" s="24" t="s">
-        <v>1222</v>
+      <c r="A232" s="22" t="s">
+        <v>1206</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>808</v>
@@ -9867,8 +9867,8 @@
       <c r="L232" s="1"/>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A233" s="24" t="s">
-        <v>1223</v>
+      <c r="A233" s="22" t="s">
+        <v>1207</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>812</v>
@@ -9891,8 +9891,8 @@
       <c r="L233" s="1"/>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A234" s="24" t="s">
-        <v>1224</v>
+      <c r="A234" s="22" t="s">
+        <v>1208</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>816</v>
@@ -9915,8 +9915,8 @@
       <c r="L234" s="1"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A235" s="24" t="s">
-        <v>1225</v>
+      <c r="A235" s="22" t="s">
+        <v>1209</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>818</v>
@@ -9939,8 +9939,8 @@
       <c r="L235" s="1"/>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A236" s="24" t="s">
-        <v>1226</v>
+      <c r="A236" s="22" t="s">
+        <v>1210</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>822</v>
@@ -9963,8 +9963,8 @@
       <c r="L236" s="1"/>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A237" s="24" t="s">
-        <v>1227</v>
+      <c r="A237" s="22" t="s">
+        <v>1211</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>826</v>
@@ -9987,8 +9987,8 @@
       <c r="L237" s="1"/>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A238" s="24" t="s">
-        <v>1228</v>
+      <c r="A238" s="22" t="s">
+        <v>1212</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>830</v>
@@ -10011,8 +10011,8 @@
       <c r="L238" s="1"/>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A239" s="24" t="s">
-        <v>1229</v>
+      <c r="A239" s="22" t="s">
+        <v>1213</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>834</v>
@@ -10035,8 +10035,8 @@
       <c r="L239" s="1"/>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A240" s="24" t="s">
-        <v>1230</v>
+      <c r="A240" s="22" t="s">
+        <v>1214</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>838</v>
@@ -10059,8 +10059,8 @@
       <c r="L240" s="1"/>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A241" s="24" t="s">
-        <v>1231</v>
+      <c r="A241" s="22" t="s">
+        <v>1215</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>842</v>
@@ -10083,8 +10083,8 @@
       <c r="L241" s="1"/>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A242" s="24" t="s">
-        <v>1232</v>
+      <c r="A242" s="22" t="s">
+        <v>1216</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>846</v>
@@ -10107,8 +10107,8 @@
       <c r="L242" s="1"/>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A243" s="24" t="s">
-        <v>1233</v>
+      <c r="A243" s="22" t="s">
+        <v>1217</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>850</v>
@@ -10131,8 +10131,8 @@
       <c r="L243" s="1"/>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A244" s="24" t="s">
-        <v>1234</v>
+      <c r="A244" s="22" t="s">
+        <v>1218</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>854</v>
@@ -10155,8 +10155,8 @@
       <c r="L244" s="1"/>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A245" s="24" t="s">
-        <v>1235</v>
+      <c r="A245" s="22" t="s">
+        <v>1219</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>858</v>
@@ -10179,8 +10179,8 @@
       <c r="L245" s="1"/>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A246" s="24" t="s">
-        <v>1236</v>
+      <c r="A246" s="22" t="s">
+        <v>1220</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>862</v>
@@ -10203,8 +10203,8 @@
       <c r="L246" s="1"/>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A247" s="24" t="s">
-        <v>1237</v>
+      <c r="A247" s="22" t="s">
+        <v>1221</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>866</v>
@@ -10227,8 +10227,8 @@
       <c r="L247" s="1"/>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A248" s="24" t="s">
-        <v>1238</v>
+      <c r="A248" s="22" t="s">
+        <v>1222</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>870</v>
@@ -10251,8 +10251,8 @@
       <c r="L248" s="1"/>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A249" s="24" t="s">
-        <v>1239</v>
+      <c r="A249" s="22" t="s">
+        <v>1223</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>874</v>
@@ -10275,8 +10275,8 @@
       <c r="L249" s="1"/>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A250" s="24" t="s">
-        <v>1240</v>
+      <c r="A250" s="22" t="s">
+        <v>1224</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>878</v>
@@ -10299,8 +10299,8 @@
       <c r="L250" s="1"/>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A251" s="24" t="s">
-        <v>1241</v>
+      <c r="A251" s="22" t="s">
+        <v>1225</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>882</v>
@@ -10323,8 +10323,8 @@
       <c r="L251" s="1"/>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A252" s="24" t="s">
-        <v>1242</v>
+      <c r="A252" s="22" t="s">
+        <v>1226</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>886</v>
@@ -10347,8 +10347,8 @@
       <c r="L252" s="1"/>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A253" s="24" t="s">
-        <v>1243</v>
+      <c r="A253" s="22" t="s">
+        <v>1227</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>890</v>
@@ -10371,8 +10371,8 @@
       <c r="L253" s="1"/>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A254" s="24" t="s">
-        <v>1244</v>
+      <c r="A254" s="22" t="s">
+        <v>1228</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>894</v>
@@ -10395,8 +10395,8 @@
       <c r="L254" s="1"/>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A255" s="24" t="s">
-        <v>1245</v>
+      <c r="A255" s="22" t="s">
+        <v>1229</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>898</v>
@@ -10419,8 +10419,8 @@
       <c r="L255" s="1"/>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A256" s="24" t="s">
-        <v>1246</v>
+      <c r="A256" s="22" t="s">
+        <v>1230</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>902</v>
@@ -10443,8 +10443,8 @@
       <c r="L256" s="1"/>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A257" s="24" t="s">
-        <v>1247</v>
+      <c r="A257" s="22" t="s">
+        <v>1231</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>904</v>
@@ -10467,8 +10467,8 @@
       <c r="L257" s="1"/>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A258" s="24" t="s">
-        <v>1248</v>
+      <c r="A258" s="22" t="s">
+        <v>1232</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>908</v>
@@ -10491,10 +10491,10 @@
       <c r="L258" s="1"/>
     </row>
     <row r="259" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A259" s="24" t="s">
-        <v>1249</v>
-      </c>
-      <c r="B259" s="26" t="s">
+      <c r="A259" s="22" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B259" s="24" t="s">
         <v>912</v>
       </c>
       <c r="C259" s="5" t="s">
@@ -10515,275 +10515,275 @@
       <c r="L259" s="1"/>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A260" s="18" t="s">
+      <c r="A260" s="16" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B260" s="17" t="s">
         <v>916</v>
       </c>
-      <c r="B260" s="19" t="s">
+      <c r="C260" s="18" t="s">
         <v>917</v>
       </c>
-      <c r="C260" s="20" t="s">
+      <c r="D260" s="16" t="s">
         <v>918</v>
       </c>
-      <c r="D260" s="18" t="s">
+      <c r="E260" s="17" t="s">
         <v>919</v>
       </c>
-      <c r="E260" s="19" t="s">
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A261" s="16" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B261" s="17" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A261" s="18" t="s">
+      <c r="C261" s="18" t="s">
         <v>921</v>
       </c>
-      <c r="B261" s="19" t="s">
+      <c r="D261" s="16" t="s">
         <v>922</v>
       </c>
-      <c r="C261" s="20" t="s">
+      <c r="E261" s="17" t="s">
         <v>923</v>
       </c>
-      <c r="D261" s="18" t="s">
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A262" s="16" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B262" s="17" t="s">
         <v>924</v>
       </c>
-      <c r="E261" s="19" t="s">
+      <c r="C262" s="18" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A262" s="18" t="s">
+      <c r="D262" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="B262" s="19" t="s">
+      <c r="E262" s="17" t="s">
         <v>927</v>
       </c>
-      <c r="C262" s="20" t="s">
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A263" s="16" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B263" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="D262" s="16" t="s">
+      <c r="C263" s="18" t="s">
         <v>929</v>
       </c>
-      <c r="E262" s="19" t="s">
+      <c r="D263" s="14" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A263" s="18" t="s">
+      <c r="E263" s="17" t="s">
         <v>931</v>
       </c>
-      <c r="B263" s="19" t="s">
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A264" s="16" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B264" s="17" t="s">
         <v>932</v>
       </c>
-      <c r="C263" s="20" t="s">
+      <c r="C264" s="18" t="s">
         <v>933</v>
       </c>
-      <c r="D263" s="16" t="s">
+      <c r="D264" s="14" t="s">
         <v>934</v>
       </c>
-      <c r="E263" s="19" t="s">
+      <c r="E264" s="17" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A264" s="18" t="s">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A265" s="16" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B265" s="17" t="s">
         <v>936</v>
       </c>
-      <c r="B264" s="19" t="s">
+      <c r="C265" s="18" t="s">
         <v>937</v>
       </c>
-      <c r="C264" s="20" t="s">
+      <c r="D265" s="14" t="s">
         <v>938</v>
       </c>
-      <c r="D264" s="16" t="s">
+      <c r="E265" s="17" t="s">
         <v>939</v>
       </c>
-      <c r="E264" s="19" t="s">
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A266" s="16" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B266" s="17" t="s">
         <v>940</v>
       </c>
-    </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A265" s="18" t="s">
+      <c r="C266" s="18" t="s">
         <v>941</v>
       </c>
-      <c r="B265" s="19" t="s">
+      <c r="D266" s="14" t="s">
         <v>942</v>
       </c>
-      <c r="C265" s="20" t="s">
+      <c r="E266" s="17" t="s">
         <v>943</v>
       </c>
-      <c r="D265" s="16" t="s">
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A267" s="16" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B267" s="17" t="s">
         <v>944</v>
       </c>
-      <c r="E265" s="19" t="s">
+      <c r="C267" s="18" t="s">
         <v>945</v>
       </c>
-    </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A266" s="18" t="s">
+      <c r="D267" s="17" t="s">
         <v>946</v>
       </c>
-      <c r="B266" s="19" t="s">
+      <c r="E267" s="17" t="s">
         <v>947</v>
       </c>
-      <c r="C266" s="20" t="s">
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A268" s="16" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B268" s="17" t="s">
         <v>948</v>
       </c>
-      <c r="D266" s="16" t="s">
+      <c r="C268" s="18" t="s">
         <v>949</v>
       </c>
-      <c r="E266" s="19" t="s">
+      <c r="D268" s="19" t="s">
         <v>950</v>
       </c>
-    </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A267" s="18" t="s">
+      <c r="E268" s="17" t="s">
         <v>951</v>
       </c>
-      <c r="B267" s="19" t="s">
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A269" s="16" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B269" s="14" t="s">
         <v>952</v>
       </c>
-      <c r="C267" s="20" t="s">
+      <c r="C269" s="18" t="s">
         <v>953</v>
       </c>
-      <c r="D267" s="19" t="s">
+      <c r="D269" s="17" t="s">
         <v>954</v>
       </c>
-      <c r="E267" s="19" t="s">
+      <c r="E269" s="17" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A268" s="18" t="s">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A270" s="16" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B270" s="17" t="s">
+        <v>948</v>
+      </c>
+      <c r="C270" s="18" t="s">
         <v>956</v>
       </c>
-      <c r="B268" s="19" t="s">
+      <c r="D270" s="17" t="s">
         <v>957</v>
       </c>
-      <c r="C268" s="20" t="s">
+      <c r="E270" s="17" t="s">
         <v>958</v>
       </c>
-      <c r="D268" s="21" t="s">
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A271" s="16" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B271" s="17" t="s">
         <v>959</v>
       </c>
-      <c r="E268" s="19" t="s">
+      <c r="C271" s="18" t="s">
         <v>960</v>
       </c>
-    </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A269" s="18" t="s">
+      <c r="D271" s="17" t="s">
         <v>961</v>
       </c>
-      <c r="B269" s="16" t="s">
+      <c r="E271" s="17" t="s">
         <v>962</v>
       </c>
-      <c r="C269" s="20" t="s">
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A272" s="16" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B272" s="17" t="s">
         <v>963</v>
       </c>
-      <c r="D269" s="19" t="s">
+      <c r="C272" s="18" t="s">
         <v>964</v>
       </c>
-      <c r="E269" s="19" t="s">
+      <c r="D272" s="15" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A270" s="18" t="s">
+      <c r="E272" s="20" t="s">
         <v>966</v>
       </c>
-      <c r="B270" s="19" t="s">
-        <v>957</v>
-      </c>
-      <c r="C270" s="20" t="s">
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="16" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B273" s="17" t="s">
         <v>967</v>
       </c>
-      <c r="D270" s="19" t="s">
+      <c r="C273" s="18" t="s">
         <v>968</v>
       </c>
-      <c r="E270" s="19" t="s">
+      <c r="D273" s="17" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A271" s="18" t="s">
+      <c r="E273" s="17" t="s">
         <v>970</v>
       </c>
-      <c r="B271" s="19" t="s">
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" s="16" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B274" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="C271" s="20" t="s">
+      <c r="C274" s="18" t="s">
         <v>972</v>
       </c>
-      <c r="D271" s="19" t="s">
+      <c r="D274" s="17" t="s">
         <v>973</v>
       </c>
-      <c r="E271" s="19" t="s">
+      <c r="E274" s="21" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A272" s="18" t="s">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" s="16" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B275" s="17" t="s">
         <v>975</v>
       </c>
-      <c r="B272" s="19" t="s">
+      <c r="C275" s="18" t="s">
         <v>976</v>
       </c>
-      <c r="C272" s="20" t="s">
+      <c r="D275" s="17" t="s">
         <v>977</v>
       </c>
-      <c r="D272" s="17" t="s">
+      <c r="E275" s="17" t="s">
         <v>978</v>
-      </c>
-      <c r="E272" s="22" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A273" s="18" t="s">
-        <v>980</v>
-      </c>
-      <c r="B273" s="19" t="s">
-        <v>981</v>
-      </c>
-      <c r="C273" s="20" t="s">
-        <v>982</v>
-      </c>
-      <c r="D273" s="19" t="s">
-        <v>983</v>
-      </c>
-      <c r="E273" s="19" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A274" s="18" t="s">
-        <v>985</v>
-      </c>
-      <c r="B274" s="19" t="s">
-        <v>986</v>
-      </c>
-      <c r="C274" s="20" t="s">
-        <v>987</v>
-      </c>
-      <c r="D274" s="19" t="s">
-        <v>988</v>
-      </c>
-      <c r="E274" s="23" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A275" s="18" t="s">
-        <v>990</v>
-      </c>
-      <c r="B275" s="19" t="s">
-        <v>991</v>
-      </c>
-      <c r="C275" s="20" t="s">
-        <v>992</v>
-      </c>
-      <c r="D275" s="19" t="s">
-        <v>993</v>
-      </c>
-      <c r="E275" s="19" t="s">
-        <v>994</v>
       </c>
     </row>
   </sheetData>

--- a/input/excel/Profile and ValueSet_ServiceRequest_Lab_16.01.2026/SRLabResearchs.xlsx
+++ b/input/excel/Profile and ValueSet_ServiceRequest_Lab_16.01.2026/SRLabResearchs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\behzod_axmedov\Desktop\DHP-temp02\UZCoreServiceRequest_Lab\digital-health-ig\input\excel\Profile and ValueSet_ServiceRequest_Lab_16.01.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC856132-59B7-44C2-992F-61A5BFBADFAA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3BC742-4F44-4EB6-8CD9-8D7D94D56E38}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8640" yWindow="1440" windowWidth="19050" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -3804,7 +3804,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3880,6 +3880,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -10515,7 +10521,7 @@
       <c r="L259" s="1"/>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A260" s="16" t="s">
+      <c r="A260" s="22" t="s">
         <v>1234</v>
       </c>
       <c r="B260" s="17" t="s">
@@ -10532,7 +10538,7 @@
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A261" s="16" t="s">
+      <c r="A261" s="22" t="s">
         <v>1235</v>
       </c>
       <c r="B261" s="17" t="s">
@@ -10549,7 +10555,7 @@
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A262" s="16" t="s">
+      <c r="A262" s="22" t="s">
         <v>1236</v>
       </c>
       <c r="B262" s="17" t="s">
@@ -10566,7 +10572,7 @@
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A263" s="16" t="s">
+      <c r="A263" s="22" t="s">
         <v>1237</v>
       </c>
       <c r="B263" s="17" t="s">
@@ -10583,7 +10589,7 @@
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A264" s="16" t="s">
+      <c r="A264" s="22" t="s">
         <v>1238</v>
       </c>
       <c r="B264" s="17" t="s">
@@ -10600,7 +10606,7 @@
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A265" s="16" t="s">
+      <c r="A265" s="22" t="s">
         <v>1239</v>
       </c>
       <c r="B265" s="17" t="s">
@@ -10617,7 +10623,7 @@
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A266" s="16" t="s">
+      <c r="A266" s="22" t="s">
         <v>1240</v>
       </c>
       <c r="B266" s="17" t="s">
@@ -10634,7 +10640,7 @@
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A267" s="16" t="s">
+      <c r="A267" s="22" t="s">
         <v>1241</v>
       </c>
       <c r="B267" s="17" t="s">
@@ -10651,7 +10657,7 @@
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A268" s="16" t="s">
+      <c r="A268" s="22" t="s">
         <v>1242</v>
       </c>
       <c r="B268" s="17" t="s">
@@ -10668,7 +10674,7 @@
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A269" s="16" t="s">
+      <c r="A269" s="22" t="s">
         <v>1243</v>
       </c>
       <c r="B269" s="14" t="s">
@@ -10685,7 +10691,7 @@
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A270" s="16" t="s">
+      <c r="A270" s="22" t="s">
         <v>1244</v>
       </c>
       <c r="B270" s="17" t="s">
@@ -10702,7 +10708,7 @@
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A271" s="16" t="s">
+      <c r="A271" s="22" t="s">
         <v>1245</v>
       </c>
       <c r="B271" s="17" t="s">
@@ -10719,7 +10725,7 @@
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A272" s="16" t="s">
+      <c r="A272" s="22" t="s">
         <v>1246</v>
       </c>
       <c r="B272" s="17" t="s">
@@ -10736,7 +10742,7 @@
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A273" s="16" t="s">
+      <c r="A273" s="22" t="s">
         <v>1247</v>
       </c>
       <c r="B273" s="17" t="s">
@@ -10753,7 +10759,7 @@
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A274" s="16" t="s">
+      <c r="A274" s="22" t="s">
         <v>1248</v>
       </c>
       <c r="B274" s="17" t="s">
@@ -10770,7 +10776,7 @@
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A275" s="16" t="s">
+      <c r="A275" s="22" t="s">
         <v>1249</v>
       </c>
       <c r="B275" s="17" t="s">
@@ -10790,6 +10796,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{8A77ECB0-9A09-435E-91AD-0F277A3E49B8}"/>
   </hyperlinks>

--- a/input/excel/Profile and ValueSet_ServiceRequest_Lab_16.01.2026/SRLabResearchs.xlsx
+++ b/input/excel/Profile and ValueSet_ServiceRequest_Lab_16.01.2026/SRLabResearchs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\behzod_axmedov\Desktop\DHP-temp02\UZCoreServiceRequest_Lab\digital-health-ig\input\excel\Profile and ValueSet_ServiceRequest_Lab_16.01.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3BC742-4F44-4EB6-8CD9-8D7D94D56E38}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEDDD82-D3E6-40EA-93EA-6A78716C1BA8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="1254">
   <si>
     <t>https://terminology.dhp.uz/fhir/core/CodeSystem/service-request-lab-research-codes-cs</t>
   </si>
@@ -3798,6 +3798,18 @@
   </si>
   <si>
     <t>lab-258</t>
+  </si>
+  <si>
+    <t>lab-P</t>
+  </si>
+  <si>
+    <t>Gepatit</t>
+  </si>
+  <si>
+    <t>Гепатит</t>
+  </si>
+  <si>
+    <t>Hepatitis</t>
   </si>
 </sst>
 </file>
@@ -3952,7 +3964,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4024,6 +4036,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -4305,7 +4322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L275"/>
+  <dimension ref="A1:L276"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.140625" customWidth="1"/>
@@ -10522,273 +10539,288 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" s="22" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B260" s="17" t="s">
-        <v>916</v>
-      </c>
-      <c r="C260" s="18" t="s">
-        <v>917</v>
-      </c>
-      <c r="D260" s="16" t="s">
-        <v>918</v>
-      </c>
-      <c r="E260" s="17" t="s">
-        <v>919</v>
+        <v>1250</v>
+      </c>
+      <c r="B260" s="27"/>
+      <c r="C260" s="28" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D260" s="29" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E260" s="29" t="s">
+        <v>1253</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" s="22" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B261" s="17" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C261" s="18" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="D261" s="16" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E261" s="17" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" s="22" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B262" s="17" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C262" s="18" t="s">
-        <v>925</v>
-      </c>
-      <c r="D262" s="14" t="s">
-        <v>926</v>
+        <v>921</v>
+      </c>
+      <c r="D262" s="16" t="s">
+        <v>922</v>
       </c>
       <c r="E262" s="17" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" s="22" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B263" s="17" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="C263" s="18" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D263" s="14" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="E263" s="17" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" s="22" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B264" s="17" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C264" s="18" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D264" s="14" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E264" s="17" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" s="22" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B265" s="17" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C265" s="18" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="D265" s="14" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="E265" s="17" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" s="22" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B266" s="17" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C266" s="18" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="D266" s="14" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="E266" s="17" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" s="22" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B267" s="17" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C267" s="18" t="s">
-        <v>945</v>
-      </c>
-      <c r="D267" s="17" t="s">
-        <v>946</v>
+        <v>941</v>
+      </c>
+      <c r="D267" s="14" t="s">
+        <v>942</v>
       </c>
       <c r="E267" s="17" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" s="22" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B268" s="17" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="C268" s="18" t="s">
-        <v>949</v>
-      </c>
-      <c r="D268" s="19" t="s">
-        <v>950</v>
+        <v>945</v>
+      </c>
+      <c r="D268" s="17" t="s">
+        <v>946</v>
       </c>
       <c r="E268" s="17" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" s="22" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B269" s="14" t="s">
-        <v>952</v>
+        <v>1242</v>
+      </c>
+      <c r="B269" s="17" t="s">
+        <v>948</v>
       </c>
       <c r="C269" s="18" t="s">
-        <v>953</v>
-      </c>
-      <c r="D269" s="17" t="s">
-        <v>954</v>
+        <v>949</v>
+      </c>
+      <c r="D269" s="19" t="s">
+        <v>950</v>
       </c>
       <c r="E269" s="17" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" s="22" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B270" s="17" t="s">
-        <v>948</v>
+        <v>1243</v>
+      </c>
+      <c r="B270" s="14" t="s">
+        <v>952</v>
       </c>
       <c r="C270" s="18" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D270" s="17" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="E270" s="17" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" s="22" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B271" s="17" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="C271" s="18" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="D271" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="E271" s="17" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" s="22" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B272" s="17" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C272" s="18" t="s">
-        <v>964</v>
-      </c>
-      <c r="D272" s="15" t="s">
-        <v>965</v>
-      </c>
-      <c r="E272" s="20" t="s">
-        <v>966</v>
+        <v>960</v>
+      </c>
+      <c r="D272" s="17" t="s">
+        <v>961</v>
+      </c>
+      <c r="E272" s="17" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="22" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B273" s="17" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C273" s="18" t="s">
-        <v>968</v>
-      </c>
-      <c r="D273" s="17" t="s">
-        <v>969</v>
-      </c>
-      <c r="E273" s="17" t="s">
-        <v>970</v>
+        <v>964</v>
+      </c>
+      <c r="D273" s="15" t="s">
+        <v>965</v>
+      </c>
+      <c r="E273" s="20" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="22" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B274" s="17" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C274" s="18" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="D274" s="17" t="s">
-        <v>973</v>
-      </c>
-      <c r="E274" s="21" t="s">
-        <v>974</v>
+        <v>969</v>
+      </c>
+      <c r="E274" s="17" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="22" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B275" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="C275" s="18" t="s">
+        <v>972</v>
+      </c>
+      <c r="D275" s="17" t="s">
+        <v>973</v>
+      </c>
+      <c r="E275" s="21" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="22" t="s">
         <v>1249</v>
       </c>
-      <c r="B275" s="17" t="s">
+      <c r="B276" s="17" t="s">
         <v>975</v>
       </c>
-      <c r="C275" s="18" t="s">
+      <c r="C276" s="18" t="s">
         <v>976</v>
       </c>
-      <c r="D275" s="17" t="s">
+      <c r="D276" s="17" t="s">
         <v>977</v>
       </c>
-      <c r="E275" s="17" t="s">
+      <c r="E276" s="17" t="s">
         <v>978</v>
       </c>
     </row>
